--- a/output/Plan/gpt-5-2025-08-07/task_analysis_results_singlepass_Plan_gpt-5-2025-08-07_trip.xlsx
+++ b/output/Plan/gpt-5-2025-08-07/task_analysis_results_singlepass_Plan_gpt-5-2025-08-07_trip.xlsx
@@ -1517,7 +1517,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>{"itinerary":[{"day_range":"Day 1-2","place":"Riga"},{"day_range":"Day 2-7","place":"Istanbul"},{"day_range":"Day 7-13","place":"Krakow"},{"day_range":"Day 13-15","place":"Warsaw"},{"day_range":"Day 15-21","place":"Reykjavik"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-2", "place": "Riga"}, {"day_range": "Day 2-7", "place": "Istanbul"}, {"day_range": "Day 7-13", "place": "Krakow"}, {"day_range": "Day 13-15", "place": "Warsaw"}, {"day_range": "Day 15-21", "place": "Reykjavik"}]}</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>{"itinerary":[{"day_range":"Day 1-3","place":"Vilnius"},{"day_range":"Day 3-7","place":"Frankfurt"},{"day_range":"Day 7-9","place":"Stuttgart"},{"day_range":"Day 9-10","place":"London"},{"day_range":"Day 10-11","place":"Santorini"},{"day_range":"Day 11-13","place":"Dublin"},{"day_range":"Day 13-17","place":"Seville"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-3", "place": "Vilnius"}, {"day_range": "Day 3-7", "place": "Frankfurt"}, {"day_range": "Day 7-9", "place": "Stuttgart"}, {"day_range": "Day 9-10", "place": "London"}, {"day_range": "Day 10-11", "place": "Santorini"}, {"day_range": "Day 11-13", "place": "Dublin"}, {"day_range": "Day 13-17", "place": "Seville"}]}</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-5", "place": "Edinburgh"}, {"day_range": "Day 5-8", "place": "Amsterdam"}, {"day_range": "Day 8-12", "place": "Vienna"}, {"day_range": "Day 12-16", "place": "Reykjavik"}, {"day_range": "Day 16-19", "place": "Berlin"}, {"day_range": "Day 19-23", "place": "Brussels"}]}</t>
+          <t>{"itinerary":[{"day_range":"Day 1-5","place":"Edinburgh"},{"day_range":"Day 5-8","place":"Amsterdam"},{"day_range":"Day 8-12","place":"Vienna"},{"day_range":"Day 12-16","place":"Reykjavik"},{"day_range":"Day 16-19","place":"Berlin"},{"day_range":"Day 19-23","place":"Brussels"}]}</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>{"itinerary":[{"day_range":"Day 1-3","place":"London"},{"day_range":"Day 3-7","place":"Milan"},{"day_range":"Day 7-8","place":"Zurich"},{"day_range":"Day 8-9","place":"Stockholm"},{"day_range":"Day 9-13","place":"Reykjavik"},{"day_range":"Day 13-17","place":"Stuttgart"},{"day_range":"Day 17-21","place":"Hamburg"},{"day_range":"Day 21-22","place":"Bucharest"},{"day_range":"Day 22-25","place":"Barcelona"},{"day_range":"Day 25-28","place":"Tallinn"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-3", "place": "London"}, {"day_range": "Day 3-7", "place": "Milan"}, {"day_range": "Day 7-8", "place": "Zurich"}, {"day_range": "Day 8-9", "place": "Stockholm"}, {"day_range": "Day 9-13", "place": "Reykjavik"}, {"day_range": "Day 13-17", "place": "Stuttgart"}, {"day_range": "Day 17-21", "place": "Hamburg"}, {"day_range": "Day 21-22", "place": "Bucharest"}, {"day_range": "Day 22-25", "place": "Barcelona"}, {"day_range": "Day 25-28", "place": "Tallinn"}]}</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-3", "place": "Nice"}, {"day_range": "Day 3-4", "place": "Reykjavik"}, {"day_range": "Day 4-5", "place": "Stockholm"}, {"day_range": "Day 5-7", "place": "Split"}, {"day_range": "Day 7-8", "place": "Copenhagen"}, {"day_range": "Day 8-11", "place": "Venice"}, {"day_range": "Day 11-13", "place": "Vienna"}, {"day_range": "Day 13-17", "place": "Porto"}]}</t>
+          <t>{"itinerary":[{"day_range":"Day 1-3","place":"Nice"},{"day_range":"Day 3-4","place":"Reykjavik"},{"day_range":"Day 4-5","place":"Stockholm"},{"day_range":"Day 5-7","place":"Split"},{"day_range":"Day 7-8","place":"Copenhagen"},{"day_range":"Day 8-11","place":"Venice"},{"day_range":"Day 11-13","place":"Vienna"},{"day_range":"Day 13-17","place":"Porto"}]}</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-7", "place": "Manchester"}, {"day_range": "Day 7-10", "place": "Madrid"}, {"day_range": "Day 10-11", "place": "Vienna"}, {"day_range": "Day 11-15", "place": "Stuttgart"}]}</t>
+          <t>{"itinerary":[{"day_range":"Day 1-7","place":"Manchester"},{"day_range":"Day 7-10","place":"Madrid"},{"day_range":"Day 10-11","place":"Vienna"},{"day_range":"Day 11-15","place":"Stuttgart"}]}</t>
         </is>
       </c>
     </row>
@@ -2144,18 +2144,18 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Failed to solve within max passes</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="E24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-4", "place": "Lyon"}, {"day_range": "Day 4-8", "place": "Paris"}, {"day_range": "Day 8-12", "place": "Copenhagen"}, {"day_range": "Day 12-13", "place": "Santorini"}, {"day_range": "Day 13-17", "place": "Oslo"}, {"day_range": "Day 17-18", "place": "Krakow"}, {"day_range": "Day 18-19", "place": "Warsaw"}, {"day_range": "Day 19-23", "place": "Helsinki"}, {"day_range": "Day 23-24", "place": "Riga"}, {"day_range": "Day 24-25", "place": "Tallinn"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-4", "place": "Lyon"}, {"day_range": "Day 4-8", "place": "Paris"}, {"day_range": "Day 8-12", "place": "Copenhagen"}, {"day_range": "Day 12-13", "place": "Santorini"}, {"day_range": "Day 13-17", "place": "Oslo"}, {"day_range": "Day 17-18", "place": "Krakow"}, {"day_range": "Day 18-22", "place": "Helsinki"}, {"day_range": "Day 22-23", "place": "Warsaw"}, {"day_range": "Day 23-24", "place": "Riga"}, {"day_range": "Day 24-25", "place": "Tallinn"}]}</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-6", "place": "ATHENS"}, {"day_range": "Day 6-11", "place": "ZURICH"}, {"day_range": "Day 11-16", "place": "VALENCIA"}, {"day_range": "Day 16-20", "place": "NAPLES"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-6", "place": "Athens"}, {"day_range": "Day 6-11", "place": "Zurich"}, {"day_range": "Day 11-16", "place": "Valencia"}, {"day_range": "Day 16-20", "place": "Naples"}]}</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-5", "place": "Naples"}, {"day_range": "Day 5-11", "place": "Vienna"}, {"day_range": "Day 11-17", "place": "Vilnius"}]}</t>
+          <t>{"itinerary":[{"day_range":"Day 1-5","place":"Naples"},{"day_range":"Day 5-11","place":"Vienna"},{"day_range":"Day 11-17","place":"Vilnius"}]}</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>{"itinerary":[{"day_range":"Day 1-4","place":"Dubrovnik"},{"day_range":"Day 4-8","place":"Munich"},{"day_range":"Day 8-9","place":"Krakow"},{"day_range":"Day 9-11","place":"Split"},{"day_range":"Day 11-13","place":"Milan"},{"day_range":"Day 13-16","place":"Porto"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-4", "place": "Dubrovnik"}, {"day_range": "Day 4-8", "place": "Munich"}, {"day_range": "Day 8-9", "place": "Krakow"}, {"day_range": "Day 9-11", "place": "Split"}, {"day_range": "Day 11-13", "place": "Milan"}, {"day_range": "Day 13-16", "place": "Porto"}]}</t>
         </is>
       </c>
     </row>
@@ -2637,18 +2637,18 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Failed to solve within max passes</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="E41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-2", "place": "Bucharest"}, {"day_range": "Day 2-4", "place": "Zurich"}, {"day_range": "Day 4-10", "place": "Split"}, {"day_range": "Day 10-11", "place": "Helsinki"}, {"day_range": "Day 11-12", "place": "Hamburg"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-3", "place": "Zurich"}, {"day_range": "Day 3-4", "place": "Helsinki"}, {"day_range": "Day 4-10", "place": "Split"}, {"day_range": "Day 10-11", "place": "Hamburg"}, {"day_range": "Day 11-12", "place": "Bucharest"}]}</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>{"itinerary":[{"day_range":"Day 1-3","place":"Naples"},{"day_range":"Day 3-9","place":"Milan"},{"day_range":"Day 9-12","place":"Seville"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-3", "place": "Naples"}, {"day_range": "Day 3-9", "place": "Milan"}, {"day_range": "Day 9-12", "place": "Seville"}]}</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-5", "place": "Santorini"}, {"day_range": "Day 5-8", "place": "Naples"}, {"day_range": "Day 8-11", "place": "Athens"}, {"day_range": "Day 11-15", "place": "Copenhagen"}, {"day_range": "Day 15-17", "place": "Dubrovnik"}, {"day_range": "Day 17-21", "place": "Munich"}, {"day_range": "Day 21-22", "place": "Prague"}, {"day_range": "Day 22-25", "place": "Brussels"}, {"day_range": "Day 25-27", "place": "Geneva"}, {"day_range": "Day 27-28", "place": "Mykonos"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-5", "place": "Santorini"}, {"day_range": "Day 5-8", "place": "Naples"}, {"day_range": "Day 8-11", "place": "Athens"}, {"day_range": "Day 11-15", "place": "Copenhagen"}, {"day_range": "Day 15-16", "place": "Prague"}, {"day_range": "Day 16-19", "place": "Brussels"}, {"day_range": "Day 19-23", "place": "Munich"}, {"day_range": "Day 23-25", "place": "Dubrovnik"}, {"day_range": "Day 25-27", "place": "Geneva"}, {"day_range": "Day 27-28", "place": "Mykonos"}]}</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>{"itinerary":[{"day_range":"Day 1-4","place":"Valencia"},{"day_range":"Day 4-7","place":"Naples"},{"day_range":"Day 7-10","place":"Manchester"},{"day_range":"Day 10-12","place":"Oslo"},{"day_range":"Day 12-13","place":"Vilnius"},{"day_range":"Day 13-16","place":"Frankfurt"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-4", "place": "Valencia"}, {"day_range": "Day 4-7", "place": "Naples"}, {"day_range": "Day 7-10", "place": "Manchester"}, {"day_range": "Day 10-12", "place": "Oslo"}, {"day_range": "Day 12-13", "place": "Vilnius"}, {"day_range": "Day 13-16", "place": "Frankfurt"}]}</t>
         </is>
       </c>
     </row>
@@ -2956,18 +2956,18 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Failed to solve within max passes</t>
         </is>
       </c>
       <c r="E52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-4", "place": "Tallinn"}, {"day_range": "Day 4-6", "place": "Munich"}, {"day_range": "Day 6-8", "place": "Venice"}, {"day_range": "Day 8-10", "place": "Santorini"}, {"day_range": "Day 10-14", "place": "Bucharest"}, {"day_range": "Day 14-15", "place": "Valencia"}, {"day_range": "Day 15-17", "place": "Porto"}, {"day_range": "Day 17-19", "place": "Manchester"}, {"day_range": "Day 19-23", "place": "Vienna"}, {"day_range": "Day 23-24", "place": "Reykjavik"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-4", "place": "Tallinn"}, {"day_range": "Day 4-6", "place": "Munich"}, {"day_range": "Day 6-8", "place": "Venice"}, {"day_range": "Day 8-10", "place": "Santorini"}, {"day_range": "Day 10-12", "place": "Manchester"}, {"day_range": "Day 12-14", "place": "Porto"}, {"day_range": "Day 14-15", "place": "Valencia"}, {"day_range": "Day 15-19", "place": "Bucharest"}, {"day_range": "Day 19-23", "place": "Vienna"}, {"day_range": "Day 23-24", "place": "Reykjavik"}]}</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-3", "place": "Porto"}, {"day_range": "Day 3-7", "place": "Paris"}, {"day_range": "Day 7-9", "place": "Florence"}, {"day_range": "Day 9-13", "place": "Munich"}, {"day_range": "Day 13-15", "place": "Warsaw"}, {"day_range": "Day 15-19", "place": "Nice"}, {"day_range": "Day 19-20", "place": "Vienna"}]}</t>
+          <t>{"itinerary":[{"day_range":"Day 1-3","place":"Porto"},{"day_range":"Day 3-7","place":"Paris"},{"day_range":"Day 7-9","place":"Florence"},{"day_range":"Day 9-13","place":"Munich"},{"day_range":"Day 13-15","place":"Warsaw"},{"day_range":"Day 15-19","place":"Nice"},{"day_range":"Day 19-20","place":"Vienna"}]}</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-2", "place": "Prague"}, {"day_range": "Day 2-6", "place": "Stockholm"}, {"day_range": "Day 6-8", "place": "Berlin"}, {"day_range": "Day 8-12", "place": "Tallinn"}]}</t>
+          <t>{"itinerary":[{"day_range":"Day 1-2","place":"Prague"},{"day_range":"Day 2-6","place":"Stockholm"},{"day_range":"Day 6-8","place":"Berlin"},{"day_range":"Day 8-12","place":"Tallinn"}]}</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-2", "place": "Salzburg"}, {"day_range": "Day 2-5", "place": "Hamburg"}, {"day_range": "Day 5-9", "place": "Venice"}, {"day_range": "Day 9-11", "place": "Nice"}, {"day_range": "Day 11-15", "place": "Zurich"}, {"day_range": "Day 15-18", "place": "Bucharest"}, {"day_range": "Day 18-21", "place": "Copenhagen"}, {"day_range": "Day 21-22", "place": "Brussels"}, {"day_range": "Day 22-25", "place": "Naples"}]}</t>
+          <t>{"itinerary":[{"day_range":"Day 1-2","place":"Salzburg"},{"day_range":"Day 2-5","place":"Hamburg"},{"day_range":"Day 5-9","place":"Venice"},{"day_range":"Day 9-11","place":"Nice"},{"day_range":"Day 11-15","place":"Zurich"},{"day_range":"Day 15-18","place":"Bucharest"},{"day_range":"Day 18-21","place":"Copenhagen"},{"day_range":"Day 21-22","place":"Brussels"},{"day_range":"Day 22-25","place":"Naples"}]}</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>{"itinerary":[{"day_range":"Day 1-3","place":"Edinburgh"},{"day_range":"Day 3-4","place":"Riga"},{"day_range":"Day 4-8","place":"Tallinn"},{"day_range":"Day 8-12","place":"Vilnius"},{"day_range":"Day 12-13","place":"Helsinki"},{"day_range":"Day 13-17","place":"Budapest"},{"day_range":"Day 17-20","place":"Geneva"},{"day_range":"Day 20-24","place":"Porto"},{"day_range":"Day 24-25","place":"Oslo"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-3", "place": "Edinburgh"}, {"day_range": "Day 3-4", "place": "Riga"}, {"day_range": "Day 4-8", "place": "Tallinn"}, {"day_range": "Day 8-12", "place": "Vilnius"}, {"day_range": "Day 12-13", "place": "Helsinki"}, {"day_range": "Day 13-17", "place": "Budapest"}, {"day_range": "Day 17-20", "place": "Geneva"}, {"day_range": "Day 20-24", "place": "Porto"}, {"day_range": "Day 24-25", "place": "Oslo"}]}</t>
         </is>
       </c>
     </row>
@@ -3420,18 +3420,18 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Failed to solve within max passes</t>
         </is>
       </c>
       <c r="E68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-4", "place": "Reykjavik"}, {"day_range": "Day 4-8", "place": "Stuttgart"}, {"day_range": "Day 8-12", "place": "Manchester"}, {"day_range": "Day 12-13", "place": "Istanbul"}, {"day_range": "Day 13-16", "place": "Riga"}, {"day_range": "Day 16-19", "place": "Bucharest"}, {"day_range": "Day 19-20", "place": "Vienna"}, {"day_range": "Day 20-23", "place": "Florence"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-4", "place": "Florence"}, {"day_range": "Day 4-5", "place": "Vienna"}, {"day_range": "Day 5-8", "place": "Reykjavik"}, {"day_range": "Day 8-12", "place": "Stuttgart"}, {"day_range": "Day 12-13", "place": "Istanbul"}, {"day_range": "Day 13-16", "place": "Riga"}, {"day_range": "Day 16-19", "place": "Bucharest"}, {"day_range": "Day 19-23", "place": "Manchester"}]}</t>
         </is>
       </c>
     </row>
@@ -3478,18 +3478,18 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Failed to solve within max passes</t>
+          <t>Exact match</t>
         </is>
       </c>
       <c r="E70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-5", "place": "Vienna"}, {"day_range": "Day 5-9", "place": "Prague"}, {"day_range": "Day 9-11", "place": "Amsterdam"}, {"day_range": "Day 11-13", "place": "Split"}, {"day_range": "Day 13-14", "place": "Munich"}, {"day_range": "Day 14-15", "place": "Istanbul"}, {"day_range": "Day 15-16", "place": "Riga"}, {"day_range": "Day 16-17", "place": "Stockholm"}, {"day_range": "Day 17-18", "place": "Brussels"}, {"day_range": "Day 18-20", "place": "Seville"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-5", "place": "Vienna"}, {"day_range": "Day 5-9", "place": "Prague"}, {"day_range": "Day 9-10", "place": "Istanbul"}, {"day_range": "Day 10-11", "place": "Munich"}, {"day_range": "Day 11-13", "place": "Split"}, {"day_range": "Day 13-15", "place": "Amsterdam"}, {"day_range": "Day 15-16", "place": "Riga"}, {"day_range": "Day 16-17", "place": "Stockholm"}, {"day_range": "Day 17-18", "place": "Brussels"}, {"day_range": "Day 18-20", "place": "Seville"}]}</t>
         </is>
       </c>
     </row>
@@ -3623,18 +3623,18 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Failed to solve within max passes</t>
         </is>
       </c>
       <c r="E75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>{"itinerary":[{"day_range":"Day 1-4","place":"Madrid"},{"day_range":"Day 4-5","place":"Seville"},{"day_range":"Day 5-7","place":"Porto"},{"day_range":"Day 7-13","place":"Stuttgart"}]}</t>
+          <t>{"itinerary":[{"day_range":"Day 1-2","place":"Seville"},{"day_range":"Day 2-5","place":"Madrid"},{"day_range":"Day 5-7","place":"Porto"},{"day_range":"Day 7-13","place":"Stuttgart"}]}</t>
         </is>
       </c>
     </row>
@@ -3681,18 +3681,18 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Failed to solve within max passes</t>
         </is>
       </c>
       <c r="E77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-4", "place": "Mykonos"}, {"day_range": "Day 4-7", "place": "Naples"}, {"day_range": "Day 7-9", "place": "Venice"}, {"day_range": "Day 9-11", "place": "Istanbul"}, {"day_range": "Day 11-15", "place": "Dublin"}, {"day_range": "Day 15-17", "place": "Frankfurt"}, {"day_range": "Day 17-20", "place": "Krakow"}, {"day_range": "Day 20-21", "place": "Brussels"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-4", "place": "Mykonos"}, {"day_range": "Day 4-7", "place": "Naples"}, {"day_range": "Day 7-9", "place": "Istanbul"}, {"day_range": "Day 9-11", "place": "Venice"}, {"day_range": "Day 11-15", "place": "Dublin"}, {"day_range": "Day 15-17", "place": "Frankfurt"}, {"day_range": "Day 17-20", "place": "Krakow"}, {"day_range": "Day 20-21", "place": "Brussels"}]}</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-2", "place": "Brussels"}, {"day_range": "Day 2-5", "place": "Lisbon"}, {"day_range": "Day 5-7", "place": "Venice"}, {"day_range": "Day 7-11", "place": "Madrid"}, {"day_range": "Day 11-13", "place": "Santorini"}, {"day_range": "Day 13-15", "place": "London"}, {"day_range": "Day 15-17", "place": "Reykjavik"}]}</t>
+          <t>{"itinerary":[{"day_range":"Day 1-2","place":"Brussels"},{"day_range":"Day 2-5","place":"Lisbon"},{"day_range":"Day 5-7","place":"Venice"},{"day_range":"Day 7-11","place":"Madrid"},{"day_range":"Day 11-13","place":"Santorini"},{"day_range":"Day 13-15","place":"London"},{"day_range":"Day 15-17","place":"Reykjavik"}]}</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-2", "place": "Florence"}, {"day_range": "Day 2-6", "place": "Munich"}, {"day_range": "Day 6-10", "place": "Krakow"}, {"day_range": "Day 10-14", "place": "Vilnius"}, {"day_range": "Day 14-18", "place": "Oslo"}, {"day_range": "Day 18-22", "place": "Hamburg"}, {"day_range": "Day 22-25", "place": "Frankfurt"}, {"day_range": "Day 25-29", "place": "Istanbul"}, {"day_range": "Day 29-31", "place": "Stockholm"}, {"day_range": "Day 31-32", "place": "Santorini"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-5", "place": "Krakow"}, {"day_range": "Day 5-9", "place": "Vilnius"}, {"day_range": "Day 9-12", "place": "Frankfurt"}, {"day_range": "Day 12-13", "place": "Florence"}, {"day_range": "Day 13-17", "place": "Munich"}, {"day_range": "Day 17-21", "place": "Hamburg"}, {"day_range": "Day 21-25", "place": "Oslo"}, {"day_range": "Day 25-29", "place": "Istanbul"}, {"day_range": "Day 29-31", "place": "Stockholm"}, {"day_range": "Day 31-32", "place": "Santorini"}]}</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>{"itinerary": [{"day_range": "Day 1-5", "place": "Berlin"}, {"day_range": "Day 5-7", "place": "Split"}, {"day_range": "Day 7-11", "place": "Lyon"}, {"day_range": "Day 11-13", "place": "Lisbon"}, {"day_range": "Day 13-15", "place": "Bucharest"}, {"day_range": "Day 15-19", "place": "Riga"}, {"day_range": "Day 19-22", "place": "Tallinn"}]}</t>
+          <t>{"itinerary":[{"day_range":"Day 1-5","place":"Berlin"},{"day_range":"Day 5-7","place":"Split"},{"day_range":"Day 7-11","place":"Lyon"},{"day_range":"Day 11-13","place":"Lisbon"},{"day_range":"Day 13-15","place":"Bucharest"},{"day_range":"Day 15-19","place":"Riga"},{"day_range":"Day 19-22","place":"Tallinn"}]}</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>{"itinerary":[{"day_range":"Day 1-4","place":"Stuttgart"},{"day_range":"Day 4-6","place":"Split"},{"day_range":"Day 6-10","place":"Helsinki"},{"day_range":"Day 10-13","place":"Brussels"},{"day_range":"Day 13-15","place":"Bucharest"},{"day_range":"Day 15-19","place":"London"},{"day_range":"Day 19-20","place":"Mykonos"},{"day_range":"Day 20-21","place":"Madrid"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-4", "place": "Stuttgart"}, {"day_range": "Day 4-6", "place": "Split"}, {"day_range": "Day 6-10", "place": "Helsinki"}, {"day_range": "Day 10-13", "place": "Brussels"}, {"day_range": "Day 13-15", "place": "Bucharest"}, {"day_range": "Day 15-19", "place": "London"}, {"day_range": "Day 19-20", "place": "Mykonos"}, {"day_range": "Day 20-21", "place": "Madrid"}]}</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>{"itinerary":[{"day_range":"Day 1-2","place":"Riga"},{"day_range":"Day 2-3","place":"Amsterdam"},{"day_range":"Day 3-7","place":"Mykonos"}]}</t>
+          <t>{"itinerary": [{"day_range": "Day 1-2", "place": "Riga"}, {"day_range": "Day 2-3", "place": "Amsterdam"}, {"day_range": "Day 3-7", "place": "Mykonos"}]}</t>
         </is>
       </c>
     </row>
